--- a/output/graficos_regionales_sexo_edad/plot_historia_nacional_s_isapre_a_2024_nacional.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_historia_nacional_s_isapre_a_2024_nacional.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-20 13:11</t>
+    <t xml:space="preserve">2026-08-28 15:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -480,7 +480,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>7.34</v>
+        <v>7.66</v>
       </c>
     </row>
     <row r="3">
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>7.31</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="4">
@@ -524,7 +524,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>9.24</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="7">
@@ -535,7 +535,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>9.02</v>
+        <v>9.08</v>
       </c>
     </row>
     <row r="8">
@@ -667,7 +667,7 @@
         <v>18</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>15.27</v>
+        <v>15.03</v>
       </c>
     </row>
     <row r="3">
@@ -678,7 +678,7 @@
         <v>18</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>14.7</v>
+        <v>14.62</v>
       </c>
     </row>
     <row r="4">
@@ -711,7 +711,7 @@
         <v>19</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>19.78</v>
+        <v>19.24</v>
       </c>
     </row>
     <row r="7">
@@ -722,7 +722,7 @@
         <v>19</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>18.62</v>
+        <v>18.23</v>
       </c>
     </row>
     <row r="8">
@@ -755,7 +755,7 @@
         <v>20</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>21.5</v>
+        <v>22.57</v>
       </c>
     </row>
     <row r="11">
@@ -766,7 +766,7 @@
         <v>20</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>21.61</v>
+        <v>22.13</v>
       </c>
     </row>
     <row r="12">
@@ -799,7 +799,7 @@
         <v>21</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>18.31</v>
+        <v>18.09</v>
       </c>
     </row>
     <row r="15">
@@ -810,7 +810,7 @@
         <v>21</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>18.28</v>
+        <v>18.17</v>
       </c>
     </row>
     <row r="16">
@@ -843,7 +843,7 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>13.33</v>
+        <v>13.56</v>
       </c>
     </row>
     <row r="19">
@@ -854,7 +854,7 @@
         <v>22</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>13.29</v>
+        <v>13.39</v>
       </c>
     </row>
     <row r="20">
@@ -887,7 +887,7 @@
         <v>23</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>8.17</v>
+        <v>8.55</v>
       </c>
     </row>
     <row r="23">
@@ -898,7 +898,7 @@
         <v>23</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>8.71</v>
+        <v>9.04</v>
       </c>
     </row>
     <row r="24">
@@ -931,7 +931,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>16.47</v>
+        <v>15.96</v>
       </c>
     </row>
     <row r="27">
@@ -942,7 +942,7 @@
         <v>24</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>16.09</v>
+        <v>15.82</v>
       </c>
     </row>
     <row r="28">

--- a/output/graficos_regionales_sexo_edad/plot_historia_nacional_s_isapre_a_2024_nacional.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_historia_nacional_s_isapre_a_2024_nacional.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 15:10</t>
+    <t xml:space="preserve">2026-08-29 05:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -480,7 +480,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>7.66</v>
+        <v>15.31</v>
       </c>
     </row>
     <row r="3">
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>7.35</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="4">
@@ -502,7 +502,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>6.43</v>
+        <v>12.85</v>
       </c>
     </row>
     <row r="5">
@@ -513,7 +513,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>5.97</v>
+        <v>11.93</v>
       </c>
     </row>
     <row r="6">
@@ -524,7 +524,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>9.68</v>
+        <v>19.36</v>
       </c>
     </row>
     <row r="7">
@@ -535,7 +535,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>9.08</v>
+        <v>18.16</v>
       </c>
     </row>
     <row r="8">
@@ -546,7 +546,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>7.95</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="9">
@@ -557,7 +557,7 @@
         <v>4</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>7.34</v>
+        <v>14.67</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_sexo_edad/plot_historia_nacional_s_isapre_a_2024_nacional.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_historia_nacional_s_isapre_a_2024_nacional.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-29 05:46</t>
+    <t xml:space="preserve">2026-09-08 09:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
